--- a/output/aruba_3_1_154days/llm_eval_runs_3_1_154days.xlsx
+++ b/output/aruba_3_1_154days/llm_eval_runs_3_1_154days.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-11T14:20:27</t>
+          <t>2026-05-18T14:16:08</t>
         </is>
       </c>
     </row>
